--- a/data/trans_orig/IP26C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP26C_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2007 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2007 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99732</t>
+          <t>99945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218477</t>
+          <t>218576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>32964</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>235262</t>
+          <t>234897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>246275</t>
+          <t>245695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233604</t>
+          <t>233883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>244980</t>
+          <t>245091</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>473587</t>
+          <t>473312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>488698</t>
+          <t>488512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>22323</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>21029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36546</t>
+          <t>36837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105895</t>
+          <t>105225</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117366</t>
+          <t>117081</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121956</t>
+          <t>122085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133062</t>
+          <t>133003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>231813</t>
+          <t>231522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247944</t>
+          <t>247330</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41213</t>
+          <t>41809</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61684</t>
+          <t>61423</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>33980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51616</t>
+          <t>51827</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79067</t>
+          <t>79774</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106635</t>
+          <t>107137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132413</t>
+          <t>132674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152884</t>
+          <t>152288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152364</t>
+          <t>152153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170228</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>291442</t>
+          <t>290940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319010</t>
+          <t>318303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65248</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92607</t>
+          <t>92845</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56136</t>
+          <t>55401</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80860</t>
+          <t>82080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126605</t>
+          <t>126903</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165722</t>
+          <t>164698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>586422</t>
+          <t>586184</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>613781</t>
+          <t>613347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>635695</t>
+          <t>634475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>660419</t>
+          <t>661154</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1229862</t>
+          <t>1230886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1268979</t>
+          <t>1268681</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2012 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2012 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136962</t>
+          <t>136454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141835</t>
+          <t>141831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131771</t>
+          <t>133076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139687</t>
+          <t>139785</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>272161</t>
+          <t>271824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280829</t>
+          <t>280754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>19755</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36163</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>215216</t>
+          <t>214217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226437</t>
+          <t>226103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246907</t>
+          <t>246377</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>258308</t>
+          <t>257921</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464769</t>
+          <t>464998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>481546</t>
+          <t>481682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>26340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49369</t>
+          <t>47803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130579</t>
+          <t>130445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143822</t>
+          <t>144205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132117</t>
+          <t>132231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145045</t>
+          <t>145555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>266245</t>
+          <t>267811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285787</t>
+          <t>286477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>30959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49378</t>
+          <t>49979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52625</t>
+          <t>53825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70244</t>
+          <t>70285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96949</t>
+          <t>96048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120700</t>
+          <t>120099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139018</t>
+          <t>139119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125084</t>
+          <t>123884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142922</t>
+          <t>143501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>250838</t>
+          <t>251739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>277543</t>
+          <t>277502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61927</t>
+          <t>61693</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87534</t>
+          <t>87705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67988</t>
+          <t>68057</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96061</t>
+          <t>96554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>134359</t>
+          <t>135645</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174051</t>
+          <t>174286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>615872</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>641650</t>
+          <t>641884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>648913</t>
+          <t>648420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>676986</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1274500</t>
+          <t>1274265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1314192</t>
+          <t>1312906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2016 (tasa de respuesta: 99,01%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2016 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120631</t>
+          <t>120411</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125501</t>
+          <t>125414</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114129</t>
+          <t>113213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237235</t>
+          <t>237017</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243365</t>
+          <t>243409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>17956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20092</t>
+          <t>19698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37078</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191400</t>
+          <t>191351</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202673</t>
+          <t>201982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>234953</t>
+          <t>234598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>247505</t>
+          <t>247585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>430290</t>
+          <t>431159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447276</t>
+          <t>447670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32552</t>
+          <t>33110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30726</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37428</t>
+          <t>36857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59132</t>
+          <t>58615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155711</t>
+          <t>155153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170283</t>
+          <t>170371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157846</t>
+          <t>157907</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>172508</t>
+          <t>172281</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317704</t>
+          <t>318221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>339408</t>
+          <t>339979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20547</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35990</t>
+          <t>35343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38358</t>
+          <t>37300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>45311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69831</t>
+          <t>69202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137311</t>
+          <t>137958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152754</t>
+          <t>153308</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135027</t>
+          <t>136085</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151444</t>
+          <t>152199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276855</t>
+          <t>277484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>300693</t>
+          <t>301375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53124</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78190</t>
+          <t>78767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>55483</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>82556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116934</t>
+          <t>117201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152569</t>
+          <t>152216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>618748</t>
+          <t>618171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>643814</t>
+          <t>643296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>654697</t>
+          <t>655990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682042</t>
+          <t>683063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1282914</t>
+          <t>1283267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1318549</t>
+          <t>1318282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49128</t>
+          <t>49109</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55311</t>
+          <t>55389</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54361</t>
+          <t>54269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59468</t>
+          <t>59304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106564</t>
+          <t>106116</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113905</t>
+          <t>113740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9621</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21908</t>
+          <t>22500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20027</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37021</t>
+          <t>35169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140483</t>
+          <t>140262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>151301</t>
+          <t>151735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160646</t>
+          <t>160054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172933</t>
+          <t>173051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304832</t>
+          <t>306684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>321826</t>
+          <t>322184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43146</t>
+          <t>43601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40263</t>
+          <t>38897</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>63919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147537</t>
+          <t>147026</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161283</t>
+          <t>160452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169344</t>
+          <t>168889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>188859</t>
+          <t>189034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321768</t>
+          <t>321644</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>345300</t>
+          <t>346666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16595</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34597</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22450</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43752</t>
+          <t>42650</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43263</t>
+          <t>44960</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72019</t>
+          <t>73628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239670</t>
+          <t>239504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258158</t>
+          <t>257672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>261731</t>
+          <t>262833</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283033</t>
+          <t>283311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>507731</t>
+          <t>506122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>536487</t>
+          <t>534790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47668</t>
+          <t>47650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74045</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67496</t>
+          <t>67044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98738</t>
+          <t>99187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124334</t>
+          <t>123542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>166277</t>
+          <t>165872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>590105</t>
+          <t>590672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>616482</t>
+          <t>616500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662807</t>
+          <t>662358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694049</t>
+          <t>694501</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1259418</t>
+          <t>1259823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1301361</t>
+          <t>1302153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP26C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP26C_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1216</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4235</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4148</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3975</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4296</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118692</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>102964</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>99945</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>100032</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>104180</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,83%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>118692</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>335</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218576</t>
+          <t>218897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118692</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118692</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118692</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104180</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104180</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104180</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118692</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118692</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118692</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13045</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8536</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20537</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11595</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7510</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18308</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17854</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13045</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7980</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19188</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32964</t>
+          <t>32863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -1184,67 +1184,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>240026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>232534</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>244535</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>241610</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>234897</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>245695</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>235351</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>246256</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>240026</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>233883</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>245091</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>473312</t>
+          <t>473413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>488512</t>
+          <t>488525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253071</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253071</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253071</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253071</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253071</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253071</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12442</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7897</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18735</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>15508</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10467</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22323</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21976</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>12,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12442</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7808</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18726</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>21060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36837</t>
+          <t>36832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>128369</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>122076</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>132914</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,39%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>112040</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>105225</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>117081</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>105572</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>117298</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>87,84%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>128369</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>122085</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>133003</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>231522</t>
+          <t>231527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247330</t>
+          <t>247299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>140811</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>140811</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>140811</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>140811</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>140811</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>140811</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42113</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>32994</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>50942</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>50588</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41809</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>61423</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41223</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>61218</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>26,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,54%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>42113</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>33980</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>51827</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79774</t>
+          <t>78875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107137</t>
+          <t>105525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161867</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>153038</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>170986</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>143509</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>132674</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>152288</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>132879</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>152874</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>73,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>161867</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>152153</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>170000</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>79,35%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>290940</t>
+          <t>292552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318303</t>
+          <t>319202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,19%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203980</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203980</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203980</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203980</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203980</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>55776</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>80366</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>78908</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>65682</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>92845</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>65895</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>93971</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>11,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67600</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>55401</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>82080</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126903</t>
+          <t>129891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164698</t>
+          <t>164954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>648955</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>636189</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>660779</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>898</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>600121</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>586184</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>613347</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>585058</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>613134</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>88,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>86,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>648955</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>634475</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>661154</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1230886</t>
+          <t>1230630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1268681</t>
+          <t>1265693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>716555</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>716555</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>716555</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>679029</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>679029</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>679029</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1077</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>716555</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>716555</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>716555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4698</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2068</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9669</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2044</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6029</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5507</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4698</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8660</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>137038</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>132067</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>139668</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>140439</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>136454</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>141831</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>136976</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>141835</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,57%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>137038</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>133076</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>139785</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>271824</t>
+          <t>271469</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280754</t>
+          <t>280819</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>141736</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>141736</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>141736</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>142483</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>142483</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>142483</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>141736</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>141736</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>141736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14063</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21364</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12696</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7869</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19755</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7553</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19153</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,43%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14063</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9038</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>20582</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19250</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>252896</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>245595</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>257999</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>221276</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>214217</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>226103</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>214819</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>226419</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,57%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>252896</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>246377</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>257921</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464998</t>
+          <t>465272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>481682</t>
+          <t>481418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>266959</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>266959</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>266959</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>233972</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>233972</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>233972</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>266959</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>266959</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>266959</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19222</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13250</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27162</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>18869</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12838</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26598</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13218</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26984</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>12,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19222</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13016</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>26340</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29137</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47803</t>
+          <t>49143</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>139349</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>131409</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145321</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>138174</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>130445</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>144205</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>130059</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>143825</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>87,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>139349</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>132231</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>145555</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>267811</t>
+          <t>266471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286477</t>
+          <t>285604</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43301</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34073</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52923</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>39610</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30959</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>49979</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30758</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>49406</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43301</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34208</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53825</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70285</t>
+          <t>68591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96048</t>
+          <t>95390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>134408</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124786</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>143636</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>70,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>80,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>130468</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>120099</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>139119</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>120672</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>139320</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>76,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>134408</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>123884</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>143501</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>251739</t>
+          <t>252397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>277502</t>
+          <t>279196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177709</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177709</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177709</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170078</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170078</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170078</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177709</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177709</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177709</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>68407</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>96745</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,99%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>73218</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>61693</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>87705</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>60202</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>86826</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>10,41%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>81283</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>68057</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>96554</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>135645</t>
+          <t>136374</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174286</t>
+          <t>174848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>663691</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>648229</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>676567</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>912</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>630359</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>615872</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>641884</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>616751</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>643375</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>663691</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>648420</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>676917</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1274265</t>
+          <t>1273703</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1312906</t>
+          <t>1312177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744974</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744974</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744974</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>703577</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703577</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703577</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744974</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744974</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744974</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4895</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2349</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5656</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6166</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>890</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5314</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>117637</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>113632</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>118527</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>123718</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>120411</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>125414</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>119901</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>125408</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,14%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>117637</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>113213</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>118527</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>376</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237017</t>
+          <t>237411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243409</t>
+          <t>243369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118527</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118527</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118527</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>126067</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>126067</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>126067</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118527</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118527</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118527</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16042</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10478</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23625</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11610</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7325</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17956</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7093</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17981</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16042</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10476</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23463</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>19612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36209</t>
+          <t>36661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>242019</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>234436</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>247583</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>197697</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>191351</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>201982</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191326</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>202214</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>242019</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>234598</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>247585</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>431159</t>
+          <t>430707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447670</t>
+          <t>447756</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>209307</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>209307</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>209307</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22434</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31282</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>24617</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17892</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33110</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>17954</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33058</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>22434</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>16291</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>30665</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36857</t>
+          <t>37200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58615</t>
+          <t>58623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166138</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157290</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>172464</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>163646</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>155153</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>170371</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>155205</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>170309</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>86,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166138</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>157907</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>172281</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,1%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318221</t>
+          <t>318213</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>339979</t>
+          <t>339636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188263</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188263</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188263</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29285</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22082</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38161</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>26962</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19993</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35343</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19757</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35581</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>29285</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>21186</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>37300</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>45441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69202</t>
+          <t>67788</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>144100</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>135224</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>151303</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>146339</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>137958</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>153308</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>137720</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>153544</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>144100</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>136085</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>152199</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>277484</t>
+          <t>278898</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301375</t>
+          <t>301245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173385</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173385</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173385</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173385</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173385</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173385</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5994,67 +5994,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>56425</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>82320</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>65539</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>53642</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>78767</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>52926</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>78613</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>68652</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>55483</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>82556</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117201</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152216</t>
+          <t>153372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>669894</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>656226</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>682121</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>952</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>631399</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>618171</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>643296</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>618325</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>644012</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,7%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>669894</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>655990</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>683063</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1283267</t>
+          <t>1282111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1318282</t>
+          <t>1318400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1049</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>696938</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>696938</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>696938</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1056</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2334</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4408</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4415</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2122</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8402</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>9755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47846</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45772</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49097</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53096</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49109</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55389</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57750</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54269</t>
+          <t>44853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59304</t>
+          <t>50337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110845</t>
+          <t>96219</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106116</t>
+          <t>92515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113740</t>
+          <t>98774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50180</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50180</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50180</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118529</t>
+          <t>102270</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118529</t>
+          <t>102270</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118529</t>
+          <t>102270</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13024</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19595</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12262</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7564</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19037</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22500</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35169</t>
+          <t>33723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>144498</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>137927</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>149209</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>147037</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>140262</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>151735</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>167596</t>
+          <t>133168</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160054</t>
+          <t>126702</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173051</t>
+          <t>137474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>314633</t>
+          <t>277666</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>306684</t>
+          <t>269316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322184</t>
+          <t>284801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31842</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23415</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43019</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17941</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12620</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26046</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32635</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>50576</t>
+          <t>49996</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>38779</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63919</t>
+          <t>62856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>168284</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157107</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>176711</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>155131</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>147026</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>160452</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,63%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>179855</t>
+          <t>156518</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>168889</t>
+          <t>149122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>189034</t>
+          <t>162428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>334987</t>
+          <t>324802</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321644</t>
+          <t>311942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>346666</t>
+          <t>336019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31916</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22281</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42193</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25101</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16595</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34763</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31935</t>
+          <t>26556</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42650</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>58472</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>47720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73628</t>
+          <t>73339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>260729</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>250452</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>270364</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>305</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>249166</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>239504</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>257672</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>273548</t>
+          <t>228781</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262833</t>
+          <t>220699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283311</t>
+          <t>237374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>522714</t>
+          <t>489510</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>506122</t>
+          <t>474643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>534790</t>
+          <t>500262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579750</t>
+          <t>547982</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579750</t>
+          <t>547982</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579750</t>
+          <t>547982</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>79116</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>63956</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>94496</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>59719</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>73478</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>60776</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>48839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99187</t>
+          <t>73096</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>139892</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123542</t>
+          <t>122247</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165872</t>
+          <t>161261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>621356</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>605976</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>636516</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>86,51%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>846</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>604431</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>590672</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>616500</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>91,01%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>678749</t>
+          <t>566841</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662358</t>
+          <t>554521</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694501</t>
+          <t>578778</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1283180</t>
+          <t>1188196</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1259823</t>
+          <t>1166827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1302153</t>
+          <t>1205841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664150</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664150</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664150</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627617</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627617</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627617</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425695</t>
+          <t>1328088</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425695</t>
+          <t>1328088</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425695</t>
+          <t>1328088</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
